--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -90,7 +90,7 @@
     <t>人脉通天</t>
   </si>
   <si>
-    <t>直接</t>
+    <t>已联系</t>
   </si>
   <si>
     <t>李伟</t>
@@ -147,7 +147,7 @@
     <t>资金;人脉</t>
   </si>
   <si>
-    <t>想接触 · 圈内可引荐</t>
+    <t>圈内可引荐</t>
   </si>
   <si>
     <t>未联系</t>
@@ -232,7 +232,7 @@
     <t>可信度（言行一致性0-5分）  [★]</t>
   </si>
   <si>
-    <t>0-5 整数。1=点头之交，3=普通朋友，5=核心铁磁。**未联系的人填 0**。
+    <t>0-5 整数。1=点头之交（旧版的『弱认识』）、3=普通朋友、5=核心铁磁。**这一列承担『有多熟』的全部表达力**——以前的『弱认识』档已废，写 1 就是。**未联系的人填 0**。
 示例：5</t>
   </si>
   <si>
@@ -268,11 +268,11 @@
     <t>关系类型  [○]</t>
   </si>
   <si>
-    <t>三选一，决定 `我` 与此人的边怎么建（不影响搜索；任何人都可能成为某次查询的 best match）：
-  留空/直接 → 直接好友（按可信度建 Me 边，默认）
-  弱认识   → 点头之交（只建强度=1 的 Me 边）
-  未联系   → 不建 Me 边；只能通过别人的『认识』被引荐到
-示例：直接</t>
+    <t>二选一，纯事实标记：
+  留空/已联系 → 我直接联系到了这个人（按可信度建 Me 边，默认）
+  未联系     → 我还没联系到这个人；只能靠别人的『认识』列被引荐到
+**这一列只描述事实，不描述意图**。『我下次想接触谁』是 web 端搜索框里那句自然语言决定的，不要预先在表里标谁是『目标』——任何人都可能成为某次查询的最佳匹配。
+示例：已联系</t>
   </si>
   <si>
     <t>通用分隔符</t>
@@ -311,10 +311,12 @@
     <t>同一个 `公司` 字段里出现的所有人会自动成为同事（强度 4）。所以**同事不要写到『认识』里**，『认识』只用来描述跨公司的人脉（校友、前同事、合作过的对家、饭局认识等）。</t>
   </si>
   <si>
-    <t>★★ 『关系类型』怎么选</t>
-  </si>
-  <si>
-    <t>直接（默认）= 用可信度作为你和此人的边强度；弱认识 = 只建强度 1 的 Me 边，避免点头之交拉高评分；未联系 = 不建 Me 边，只依靠别人的『认识』列抵达——多跳引荐路径才能找到他。把『想接触、还没直接联系』的人都标成『未联系』；**这一档不影响搜索本身**——任何人（直接/弱/未联系）都可能是你下次自然语言查询的最佳匹配，搜索按相关性排序而非按这个标签。</t>
+    <t>★★ 『关系类型』就两档：已联系 / 未联系</t>
+  </si>
+  <si>
+    <t>二选一，纯事实标记，不是意图：  已联系（默认）= 我直接联系到了这个人，按『可信度』1-5 决定边的强度；  未联系 = 我还没联系到，不建 Me 边，只能靠别人的『认识』列被引荐到。
+旧版的『弱认识』档已废——『有多熟』完全交给『可信度』列表达，写 1 就是。
+⚠️ **这一列不要用来标『谁是我想接触的人』**。『下次想找谁』是你在 web 端搜索框里说的那句话，由 LLM 解析意图后从全表（含已联系 + 未联系）一起匹配并算路径——任何人都可能是某次查询的最佳匹配。</t>
   </si>
   <si>
     <t>★★ AI 自动补字段（v2 新机制）</t>
@@ -4244,8 +4246,8 @@
   </sheetData>
   <autoFilter ref="A1:N201"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="关系类型" prompt="直接=默认；弱认识=只建强度1边；未联系=不建 Me 边，靠他人引荐" sqref="N2:N2001">
-      <formula1>"直接,弱认识,未联系"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="关系类型" prompt="二选一，纯事实：已联系=默认（按可信度建 Me 边）；未联系=不建 Me 边，靠他人引荐。" sqref="N2:N2001">
+      <formula1>"已联系,未联系"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可信度" prompt="0-5 整数；未联系的人填 0" sqref="H2:H2001">
       <formula1>0</formula1>
@@ -5230,7 +5232,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="32" customHeight="1">
+    <row r="12" spans="1:2" ht="56" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>67</v>
       </c>

--- a/examples/template.xlsx
+++ b/examples/template.xlsx
@@ -12,14 +12,14 @@
     <sheet name="说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">联系人!$A$1:$N$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">联系人!$A$1:$M$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
   <si>
     <t>序号</t>
   </si>
@@ -60,9 +60,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>关系类型</t>
-  </si>
-  <si>
     <t>陈维国</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>人脉通天</t>
   </si>
   <si>
-    <t>已联系</t>
-  </si>
-  <si>
     <t>李伟</t>
   </si>
   <si>
@@ -147,10 +141,7 @@
     <t>资金;人脉</t>
   </si>
   <si>
-    <t>圈内可引荐</t>
-  </si>
-  <si>
-    <t>未联系</t>
+    <t>圈内可引荐 · 可信度=0 即代表未联系</t>
   </si>
   <si>
     <t>甲</t>
@@ -232,7 +223,12 @@
     <t>可信度（言行一致性0-5分）  [★]</t>
   </si>
   <si>
-    <t>0-5 整数。1=点头之交（旧版的『弱认识』）、3=普通朋友、5=核心铁磁。**这一列承担『有多熟』的全部表达力**——以前的『弱认识』档已废，写 1 就是。**未联系的人填 0**。
+    <t>★ 整张表里最关键的一列，**单列承载两件事**：
+  0 = 未联系（我还没直接接触过 → 系统不建 Me 边，靠他人引荐到达）
+  1 = 点头之交（刚加微信/见过一面/饭局认识）
+  3 = 普通朋友
+  5 = 核心铁磁
+**留空会被当成 3**，所以填表时务必显式给 0 标出未联系，不要漏填。
 示例：5</t>
   </si>
   <si>
@@ -265,16 +261,6 @@
 示例：人脉通天</t>
   </si>
   <si>
-    <t>关系类型  [○]</t>
-  </si>
-  <si>
-    <t>二选一，纯事实标记：
-  留空/已联系 → 我直接联系到了这个人（按可信度建 Me 边，默认）
-  未联系     → 我还没联系到这个人；只能靠别人的『认识』列被引荐到
-**这一列只描述事实，不描述意图**。『我下次想接触谁』是 web 端搜索框里那句自然语言决定的，不要预先在表里标谁是『目标』——任何人都可能成为某次查询的最佳匹配。
-示例：已联系</t>
-  </si>
-  <si>
     <t>通用分隔符</t>
   </si>
   <si>
@@ -311,12 +297,16 @@
     <t>同一个 `公司` 字段里出现的所有人会自动成为同事（强度 4）。所以**同事不要写到『认识』里**，『认识』只用来描述跨公司的人脉（校友、前同事、合作过的对家、饭局认识等）。</t>
   </si>
   <si>
-    <t>★★ 『关系类型』就两档：已联系 / 未联系</t>
-  </si>
-  <si>
-    <t>二选一，纯事实标记，不是意图：  已联系（默认）= 我直接联系到了这个人，按『可信度』1-5 决定边的强度；  未联系 = 我还没联系到，不建 Me 边，只能靠别人的『认识』列被引荐到。
-旧版的『弱认识』档已废——『有多熟』完全交给『可信度』列表达，写 1 就是。
-⚠️ **这一列不要用来标『谁是我想接触的人』**。『下次想找谁』是你在 web 端搜索框里说的那句话，由 LLM 解析意图后从全表（含已联系 + 未联系）一起匹配并算路径——任何人都可能是某次查询的最佳匹配。</t>
+    <t>★★ 单列承载一切：可信度 0-5</t>
+  </si>
+  <si>
+    <t>整张表里**唯一**用来表达『我和这个人的关系』的列，只填一个 0-5 的整数：
+  0 → 未联系：我还没直接接触过这个人。系统不建 Me 边，      搜索时若命中，会自动算 1-3 跳引荐路径并放在『需要引荐』段。
+  1 → 点头之交：刚加微信、饭局认识、被介绍认识但没深聊。
+  3 → 普通朋友：能直接拉群、互相有印象。
+  5 → 核心铁磁：随叫随到、深度合作、信任无保留。
+⚠️ 留空 = 默认 3，所以**未联系的人务必显式填 0**，否则会被当成普通朋友来建直边，引荐路径就推不出来了。
+⚠️ **不要预先在表里标『谁是我想接触的人』**。『下次想找谁』是 web 端搜索框里那句自然语言决定的，由 LLM 解析意图后从全表（含已联系 + 未联系）一起匹配——任何人都可能是某次查询的最佳匹配。</t>
   </si>
   <si>
     <t>★★ AI 自动补字段（v2 新机制）</t>
@@ -858,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N204"/>
+  <dimension ref="A1:M204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -872,10 +862,9 @@
     <col min="11" max="11" width="14.7109375" customWidth="1"/>
     <col min="12" max="12" width="56.7109375" customWidth="1"/>
     <col min="13" max="13" width="22.7109375" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,71 +904,65 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="H3" s="3">
         <v>4</v>
@@ -988,62 +971,56 @@
         <v>5</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1057,9 +1034,8 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-    </row>
-    <row r="6" spans="1:14">
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1073,9 +1049,8 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-    </row>
-    <row r="7" spans="1:14">
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1089,9 +1064,8 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" spans="1:14">
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1105,9 +1079,8 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-    </row>
-    <row r="9" spans="1:14">
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1121,9 +1094,8 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-    </row>
-    <row r="10" spans="1:14">
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1137,9 +1109,8 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" spans="1:14">
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1153,9 +1124,8 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-    </row>
-    <row r="12" spans="1:14">
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1169,9 +1139,8 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-    </row>
-    <row r="13" spans="1:14">
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1185,9 +1154,8 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" spans="1:14">
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1201,9 +1169,8 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" spans="1:14">
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1217,9 +1184,8 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-    </row>
-    <row r="16" spans="1:14">
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1233,9 +1199,8 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" spans="1:14">
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1249,9 +1214,8 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-    </row>
-    <row r="18" spans="1:14">
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1265,9 +1229,8 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" spans="1:14">
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1281,9 +1244,8 @@
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-    </row>
-    <row r="20" spans="1:14">
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1297,9 +1259,8 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-    </row>
-    <row r="21" spans="1:14">
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1313,9 +1274,8 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-    </row>
-    <row r="22" spans="1:14">
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1329,9 +1289,8 @@
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-    </row>
-    <row r="23" spans="1:14">
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1345,9 +1304,8 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="1:14">
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1361,9 +1319,8 @@
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-    </row>
-    <row r="25" spans="1:14">
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1377,9 +1334,8 @@
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-    </row>
-    <row r="26" spans="1:14">
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1393,9 +1349,8 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-    </row>
-    <row r="27" spans="1:14">
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1409,9 +1364,8 @@
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-    </row>
-    <row r="28" spans="1:14">
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1425,9 +1379,8 @@
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-    </row>
-    <row r="29" spans="1:14">
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1441,9 +1394,8 @@
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-    </row>
-    <row r="30" spans="1:14">
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1457,9 +1409,8 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-    </row>
-    <row r="31" spans="1:14">
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1473,9 +1424,8 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-    </row>
-    <row r="32" spans="1:14">
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1489,9 +1439,8 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-    </row>
-    <row r="33" spans="1:14">
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -1505,9 +1454,8 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-    </row>
-    <row r="34" spans="1:14">
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -1521,9 +1469,8 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-    </row>
-    <row r="35" spans="1:14">
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -1537,9 +1484,8 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-    </row>
-    <row r="36" spans="1:14">
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -1553,9 +1499,8 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-    </row>
-    <row r="37" spans="1:14">
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -1569,9 +1514,8 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-    </row>
-    <row r="38" spans="1:14">
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -1585,9 +1529,8 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-    </row>
-    <row r="39" spans="1:14">
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -1601,9 +1544,8 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-    </row>
-    <row r="40" spans="1:14">
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -1617,9 +1559,8 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-    </row>
-    <row r="41" spans="1:14">
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -1633,9 +1574,8 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-    </row>
-    <row r="42" spans="1:14">
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -1649,9 +1589,8 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-    </row>
-    <row r="43" spans="1:14">
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -1665,9 +1604,8 @@
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-    </row>
-    <row r="44" spans="1:14">
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1681,9 +1619,8 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-    </row>
-    <row r="45" spans="1:14">
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -1697,9 +1634,8 @@
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-    </row>
-    <row r="46" spans="1:14">
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -1713,9 +1649,8 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-    </row>
-    <row r="47" spans="1:14">
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -1729,9 +1664,8 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-    </row>
-    <row r="48" spans="1:14">
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1745,9 +1679,8 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-    </row>
-    <row r="49" spans="1:14">
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -1761,9 +1694,8 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-    </row>
-    <row r="50" spans="1:14">
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -1777,9 +1709,8 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-    </row>
-    <row r="51" spans="1:14">
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -1793,9 +1724,8 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-    </row>
-    <row r="52" spans="1:14">
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -1809,9 +1739,8 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-    </row>
-    <row r="53" spans="1:14">
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -1825,9 +1754,8 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-    </row>
-    <row r="54" spans="1:14">
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -1841,9 +1769,8 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-    </row>
-    <row r="55" spans="1:14">
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -1857,9 +1784,8 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-    </row>
-    <row r="56" spans="1:14">
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -1873,9 +1799,8 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
-      <c r="N56" s="7"/>
-    </row>
-    <row r="57" spans="1:14">
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -1889,9 +1814,8 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
-      <c r="N57" s="7"/>
-    </row>
-    <row r="58" spans="1:14">
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -1905,9 +1829,8 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
-    </row>
-    <row r="59" spans="1:14">
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -1921,9 +1844,8 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-    </row>
-    <row r="60" spans="1:14">
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -1937,9 +1859,8 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
-    </row>
-    <row r="61" spans="1:14">
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -1953,9 +1874,8 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="N61" s="7"/>
-    </row>
-    <row r="62" spans="1:14">
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -1969,9 +1889,8 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-    </row>
-    <row r="63" spans="1:14">
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -1985,9 +1904,8 @@
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
-      <c r="N63" s="7"/>
-    </row>
-    <row r="64" spans="1:14">
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -2001,9 +1919,8 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
-    </row>
-    <row r="65" spans="1:14">
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -2017,9 +1934,8 @@
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
-      <c r="N65" s="7"/>
-    </row>
-    <row r="66" spans="1:14">
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -2033,9 +1949,8 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
-      <c r="N66" s="7"/>
-    </row>
-    <row r="67" spans="1:14">
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -2049,9 +1964,8 @@
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
-      <c r="N67" s="7"/>
-    </row>
-    <row r="68" spans="1:14">
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -2065,9 +1979,8 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-    </row>
-    <row r="69" spans="1:14">
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -2081,9 +1994,8 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
-    </row>
-    <row r="70" spans="1:14">
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -2097,9 +2009,8 @@
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-    </row>
-    <row r="71" spans="1:14">
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -2113,9 +2024,8 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
-      <c r="N71" s="7"/>
-    </row>
-    <row r="72" spans="1:14">
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -2129,9 +2039,8 @@
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
-      <c r="N72" s="7"/>
-    </row>
-    <row r="73" spans="1:14">
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -2145,9 +2054,8 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
-    </row>
-    <row r="74" spans="1:14">
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -2161,9 +2069,8 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-    </row>
-    <row r="75" spans="1:14">
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -2177,9 +2084,8 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-    </row>
-    <row r="76" spans="1:14">
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -2193,9 +2099,8 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-    </row>
-    <row r="77" spans="1:14">
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -2209,9 +2114,8 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
-      <c r="N77" s="7"/>
-    </row>
-    <row r="78" spans="1:14">
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -2225,9 +2129,8 @@
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
-    </row>
-    <row r="79" spans="1:14">
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -2241,9 +2144,8 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-    </row>
-    <row r="80" spans="1:14">
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -2257,9 +2159,8 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-    </row>
-    <row r="81" spans="1:14">
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -2273,9 +2174,8 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-    </row>
-    <row r="82" spans="1:14">
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -2289,9 +2189,8 @@
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-    </row>
-    <row r="83" spans="1:14">
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -2305,9 +2204,8 @@
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
-      <c r="N83" s="7"/>
-    </row>
-    <row r="84" spans="1:14">
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -2321,9 +2219,8 @@
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
-    </row>
-    <row r="85" spans="1:14">
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -2337,9 +2234,8 @@
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
-      <c r="N85" s="7"/>
-    </row>
-    <row r="86" spans="1:14">
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -2353,9 +2249,8 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
-      <c r="N86" s="7"/>
-    </row>
-    <row r="87" spans="1:14">
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -2369,9 +2264,8 @@
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
-      <c r="N87" s="7"/>
-    </row>
-    <row r="88" spans="1:14">
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -2385,9 +2279,8 @@
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
-      <c r="N88" s="7"/>
-    </row>
-    <row r="89" spans="1:14">
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -2401,9 +2294,8 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-    </row>
-    <row r="90" spans="1:14">
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -2417,9 +2309,8 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
-      <c r="N90" s="7"/>
-    </row>
-    <row r="91" spans="1:14">
+    </row>
+    <row r="91" spans="1:13">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -2433,9 +2324,8 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
-      <c r="N91" s="7"/>
-    </row>
-    <row r="92" spans="1:14">
+    </row>
+    <row r="92" spans="1:13">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -2449,9 +2339,8 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-    </row>
-    <row r="93" spans="1:14">
+    </row>
+    <row r="93" spans="1:13">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -2465,9 +2354,8 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
-      <c r="N93" s="7"/>
-    </row>
-    <row r="94" spans="1:14">
+    </row>
+    <row r="94" spans="1:13">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -2481,9 +2369,8 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
-    </row>
-    <row r="95" spans="1:14">
+    </row>
+    <row r="95" spans="1:13">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -2497,9 +2384,8 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
-      <c r="N95" s="7"/>
-    </row>
-    <row r="96" spans="1:14">
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -2513,9 +2399,8 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
-    </row>
-    <row r="97" spans="1:14">
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -2529,9 +2414,8 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
-      <c r="N97" s="7"/>
-    </row>
-    <row r="98" spans="1:14">
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2545,9 +2429,8 @@
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
-      <c r="N98" s="7"/>
-    </row>
-    <row r="99" spans="1:14">
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2561,9 +2444,8 @@
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
-      <c r="N99" s="7"/>
-    </row>
-    <row r="100" spans="1:14">
+    </row>
+    <row r="100" spans="1:13">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2577,9 +2459,8 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
-      <c r="N100" s="7"/>
-    </row>
-    <row r="101" spans="1:14">
+    </row>
+    <row r="101" spans="1:13">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2593,9 +2474,8 @@
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
-      <c r="N101" s="7"/>
-    </row>
-    <row r="102" spans="1:14">
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2609,9 +2489,8 @@
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
-      <c r="N102" s="7"/>
-    </row>
-    <row r="103" spans="1:14">
+    </row>
+    <row r="103" spans="1:13">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2625,9 +2504,8 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
-      <c r="N103" s="7"/>
-    </row>
-    <row r="104" spans="1:14">
+    </row>
+    <row r="104" spans="1:13">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2641,9 +2519,8 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
-      <c r="N104" s="7"/>
-    </row>
-    <row r="105" spans="1:14">
+    </row>
+    <row r="105" spans="1:13">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2657,9 +2534,8 @@
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
-      <c r="N105" s="7"/>
-    </row>
-    <row r="106" spans="1:14">
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2673,9 +2549,8 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
-      <c r="N106" s="7"/>
-    </row>
-    <row r="107" spans="1:14">
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2689,9 +2564,8 @@
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c r="M107" s="7"/>
-      <c r="N107" s="7"/>
-    </row>
-    <row r="108" spans="1:14">
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2705,9 +2579,8 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-    </row>
-    <row r="109" spans="1:14">
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2721,9 +2594,8 @@
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-    </row>
-    <row r="110" spans="1:14">
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2737,9 +2609,8 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-    </row>
-    <row r="111" spans="1:14">
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2753,9 +2624,8 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-    </row>
-    <row r="112" spans="1:14">
+    </row>
+    <row r="112" spans="1:13">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2769,9 +2639,8 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
-      <c r="N112" s="7"/>
-    </row>
-    <row r="113" spans="1:14">
+    </row>
+    <row r="113" spans="1:13">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -2785,9 +2654,8 @@
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
-      <c r="N113" s="7"/>
-    </row>
-    <row r="114" spans="1:14">
+    </row>
+    <row r="114" spans="1:13">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -2801,9 +2669,8 @@
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
-      <c r="N114" s="7"/>
-    </row>
-    <row r="115" spans="1:14">
+    </row>
+    <row r="115" spans="1:13">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -2817,9 +2684,8 @@
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c r="M115" s="7"/>
-      <c r="N115" s="7"/>
-    </row>
-    <row r="116" spans="1:14">
+    </row>
+    <row r="116" spans="1:13">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -2833,9 +2699,8 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
-    </row>
-    <row r="117" spans="1:14">
+    </row>
+    <row r="117" spans="1:13">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -2849,9 +2714,8 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
-      <c r="N117" s="7"/>
-    </row>
-    <row r="118" spans="1:14">
+    </row>
+    <row r="118" spans="1:13">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -2865,9 +2729,8 @@
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
-    </row>
-    <row r="119" spans="1:14">
+    </row>
+    <row r="119" spans="1:13">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -2881,9 +2744,8 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-    </row>
-    <row r="120" spans="1:14">
+    </row>
+    <row r="120" spans="1:13">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -2897,9 +2759,8 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-    </row>
-    <row r="121" spans="1:14">
+    </row>
+    <row r="121" spans="1:13">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -2913,9 +2774,8 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-    </row>
-    <row r="122" spans="1:14">
+    </row>
+    <row r="122" spans="1:13">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -2929,9 +2789,8 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
-    </row>
-    <row r="123" spans="1:14">
+    </row>
+    <row r="123" spans="1:13">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -2945,9 +2804,8 @@
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
-      <c r="N123" s="7"/>
-    </row>
-    <row r="124" spans="1:14">
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -2961,9 +2819,8 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-    </row>
-    <row r="125" spans="1:14">
+    </row>
+    <row r="125" spans="1:13">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2977,9 +2834,8 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-    </row>
-    <row r="126" spans="1:14">
+    </row>
+    <row r="126" spans="1:13">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2993,9 +2849,8 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-    </row>
-    <row r="127" spans="1:14">
+    </row>
+    <row r="127" spans="1:13">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -3009,9 +2864,8 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-    </row>
-    <row r="128" spans="1:14">
+    </row>
+    <row r="128" spans="1:13">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -3025,9 +2879,8 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-    </row>
-    <row r="129" spans="1:14">
+    </row>
+    <row r="129" spans="1:13">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -3041,9 +2894,8 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-    </row>
-    <row r="130" spans="1:14">
+    </row>
+    <row r="130" spans="1:13">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -3057,9 +2909,8 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-    </row>
-    <row r="131" spans="1:14">
+    </row>
+    <row r="131" spans="1:13">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -3073,9 +2924,8 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
-      <c r="N131" s="7"/>
-    </row>
-    <row r="132" spans="1:14">
+    </row>
+    <row r="132" spans="1:13">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -3089,9 +2939,8 @@
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
-    </row>
-    <row r="133" spans="1:14">
+    </row>
+    <row r="133" spans="1:13">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -3105,9 +2954,8 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
-      <c r="N133" s="7"/>
-    </row>
-    <row r="134" spans="1:14">
+    </row>
+    <row r="134" spans="1:13">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -3121,9 +2969,8 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-    </row>
-    <row r="135" spans="1:14">
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -3137,9 +2984,8 @@
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
-      <c r="N135" s="7"/>
-    </row>
-    <row r="136" spans="1:14">
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -3153,9 +2999,8 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-    </row>
-    <row r="137" spans="1:14">
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -3169,9 +3014,8 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-    </row>
-    <row r="138" spans="1:14">
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -3185,9 +3029,8 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
-    </row>
-    <row r="139" spans="1:14">
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -3201,9 +3044,8 @@
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-    </row>
-    <row r="140" spans="1:14">
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -3217,9 +3059,8 @@
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
-    </row>
-    <row r="141" spans="1:14">
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -3233,9 +3074,8 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
-      <c r="N141" s="7"/>
-    </row>
-    <row r="142" spans="1:14">
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -3249,9 +3089,8 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
-      <c r="N142" s="7"/>
-    </row>
-    <row r="143" spans="1:14">
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -3265,9 +3104,8 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
-      <c r="N143" s="7"/>
-    </row>
-    <row r="144" spans="1:14">
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -3281,9 +3119,8 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
-      <c r="N144" s="7"/>
-    </row>
-    <row r="145" spans="1:14">
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -3297,9 +3134,8 @@
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
-      <c r="N145" s="7"/>
-    </row>
-    <row r="146" spans="1:14">
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -3313,9 +3149,8 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
-      <c r="N146" s="7"/>
-    </row>
-    <row r="147" spans="1:14">
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -3329,9 +3164,8 @@
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-    </row>
-    <row r="148" spans="1:14">
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -3345,9 +3179,8 @@
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c r="M148" s="7"/>
-      <c r="N148" s="7"/>
-    </row>
-    <row r="149" spans="1:14">
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -3361,9 +3194,8 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
-      <c r="N149" s="7"/>
-    </row>
-    <row r="150" spans="1:14">
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -3377,9 +3209,8 @@
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
-      <c r="N150" s="7"/>
-    </row>
-    <row r="151" spans="1:14">
+    </row>
+    <row r="151" spans="1:13">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -3393,9 +3224,8 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
-      <c r="N151" s="7"/>
-    </row>
-    <row r="152" spans="1:14">
+    </row>
+    <row r="152" spans="1:13">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -3409,9 +3239,8 @@
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
-      <c r="N152" s="7"/>
-    </row>
-    <row r="153" spans="1:14">
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -3425,9 +3254,8 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c r="M153" s="7"/>
-      <c r="N153" s="7"/>
-    </row>
-    <row r="154" spans="1:14">
+    </row>
+    <row r="154" spans="1:13">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -3441,9 +3269,8 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c r="M154" s="7"/>
-      <c r="N154" s="7"/>
-    </row>
-    <row r="155" spans="1:14">
+    </row>
+    <row r="155" spans="1:13">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -3457,9 +3284,8 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c r="M155" s="7"/>
-      <c r="N155" s="7"/>
-    </row>
-    <row r="156" spans="1:14">
+    </row>
+    <row r="156" spans="1:13">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -3473,9 +3299,8 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c r="M156" s="7"/>
-      <c r="N156" s="7"/>
-    </row>
-    <row r="157" spans="1:14">
+    </row>
+    <row r="157" spans="1:13">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -3489,9 +3314,8 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
-      <c r="N157" s="7"/>
-    </row>
-    <row r="158" spans="1:14">
+    </row>
+    <row r="158" spans="1:13">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -3505,9 +3329,8 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
-      <c r="N158" s="7"/>
-    </row>
-    <row r="159" spans="1:14">
+    </row>
+    <row r="159" spans="1:13">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -3521,9 +3344,8 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
-      <c r="N159" s="7"/>
-    </row>
-    <row r="160" spans="1:14">
+    </row>
+    <row r="160" spans="1:13">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -3537,9 +3359,8 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
-      <c r="N160" s="7"/>
-    </row>
-    <row r="161" spans="1:14">
+    </row>
+    <row r="161" spans="1:13">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -3553,9 +3374,8 @@
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
-      <c r="N161" s="7"/>
-    </row>
-    <row r="162" spans="1:14">
+    </row>
+    <row r="162" spans="1:13">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -3569,9 +3389,8 @@
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
-      <c r="N162" s="7"/>
-    </row>
-    <row r="163" spans="1:14">
+    </row>
+    <row r="163" spans="1:13">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -3585,9 +3404,8 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
-      <c r="N163" s="7"/>
-    </row>
-    <row r="164" spans="1:14">
+    </row>
+    <row r="164" spans="1:13">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -3601,9 +3419,8 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
-      <c r="N164" s="7"/>
-    </row>
-    <row r="165" spans="1:14">
+    </row>
+    <row r="165" spans="1:13">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -3617,9 +3434,8 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c r="M165" s="7"/>
-      <c r="N165" s="7"/>
-    </row>
-    <row r="166" spans="1:14">
+    </row>
+    <row r="166" spans="1:13">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -3633,9 +3449,8 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
-      <c r="N166" s="7"/>
-    </row>
-    <row r="167" spans="1:14">
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -3649,9 +3464,8 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
-      <c r="N167" s="7"/>
-    </row>
-    <row r="168" spans="1:14">
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -3665,9 +3479,8 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
-      <c r="N168" s="7"/>
-    </row>
-    <row r="169" spans="1:14">
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -3681,9 +3494,8 @@
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
-      <c r="N169" s="7"/>
-    </row>
-    <row r="170" spans="1:14">
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -3697,9 +3509,8 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
-      <c r="N170" s="7"/>
-    </row>
-    <row r="171" spans="1:14">
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -3713,9 +3524,8 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
-      <c r="N171" s="7"/>
-    </row>
-    <row r="172" spans="1:14">
+    </row>
+    <row r="172" spans="1:13">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -3729,9 +3539,8 @@
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
-      <c r="N172" s="7"/>
-    </row>
-    <row r="173" spans="1:14">
+    </row>
+    <row r="173" spans="1:13">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3745,9 +3554,8 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7"/>
-      <c r="N173" s="7"/>
-    </row>
-    <row r="174" spans="1:14">
+    </row>
+    <row r="174" spans="1:13">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3761,9 +3569,8 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c r="M174" s="7"/>
-      <c r="N174" s="7"/>
-    </row>
-    <row r="175" spans="1:14">
+    </row>
+    <row r="175" spans="1:13">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3777,9 +3584,8 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c r="M175" s="7"/>
-      <c r="N175" s="7"/>
-    </row>
-    <row r="176" spans="1:14">
+    </row>
+    <row r="176" spans="1:13">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3793,9 +3599,8 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c r="M176" s="7"/>
-      <c r="N176" s="7"/>
-    </row>
-    <row r="177" spans="1:14">
+    </row>
+    <row r="177" spans="1:13">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3809,9 +3614,8 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c r="M177" s="7"/>
-      <c r="N177" s="7"/>
-    </row>
-    <row r="178" spans="1:14">
+    </row>
+    <row r="178" spans="1:13">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3825,9 +3629,8 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
-      <c r="N178" s="7"/>
-    </row>
-    <row r="179" spans="1:14">
+    </row>
+    <row r="179" spans="1:13">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3841,9 +3644,8 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c r="M179" s="7"/>
-      <c r="N179" s="7"/>
-    </row>
-    <row r="180" spans="1:14">
+    </row>
+    <row r="180" spans="1:13">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3857,9 +3659,8 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
-      <c r="N180" s="7"/>
-    </row>
-    <row r="181" spans="1:14">
+    </row>
+    <row r="181" spans="1:13">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3873,9 +3674,8 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
-      <c r="N181" s="7"/>
-    </row>
-    <row r="182" spans="1:14">
+    </row>
+    <row r="182" spans="1:13">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3889,9 +3689,8 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
-      <c r="N182" s="7"/>
-    </row>
-    <row r="183" spans="1:14">
+    </row>
+    <row r="183" spans="1:13">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3905,9 +3704,8 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
-      <c r="N183" s="7"/>
-    </row>
-    <row r="184" spans="1:14">
+    </row>
+    <row r="184" spans="1:13">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3921,9 +3719,8 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
-      <c r="N184" s="7"/>
-    </row>
-    <row r="185" spans="1:14">
+    </row>
+    <row r="185" spans="1:13">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -3937,9 +3734,8 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
-      <c r="N185" s="7"/>
-    </row>
-    <row r="186" spans="1:14">
+    </row>
+    <row r="186" spans="1:13">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -3953,9 +3749,8 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c r="M186" s="7"/>
-      <c r="N186" s="7"/>
-    </row>
-    <row r="187" spans="1:14">
+    </row>
+    <row r="187" spans="1:13">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -3969,9 +3764,8 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c r="M187" s="7"/>
-      <c r="N187" s="7"/>
-    </row>
-    <row r="188" spans="1:14">
+    </row>
+    <row r="188" spans="1:13">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -3985,9 +3779,8 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c r="M188" s="7"/>
-      <c r="N188" s="7"/>
-    </row>
-    <row r="189" spans="1:14">
+    </row>
+    <row r="189" spans="1:13">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -4001,9 +3794,8 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
-      <c r="N189" s="7"/>
-    </row>
-    <row r="190" spans="1:14">
+    </row>
+    <row r="190" spans="1:13">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -4017,9 +3809,8 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
-      <c r="N190" s="7"/>
-    </row>
-    <row r="191" spans="1:14">
+    </row>
+    <row r="191" spans="1:13">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -4033,9 +3824,8 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
-      <c r="N191" s="7"/>
-    </row>
-    <row r="192" spans="1:14">
+    </row>
+    <row r="192" spans="1:13">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -4049,9 +3839,8 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
-      <c r="N192" s="7"/>
-    </row>
-    <row r="193" spans="1:14">
+    </row>
+    <row r="193" spans="1:13">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -4065,9 +3854,8 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c r="M193" s="7"/>
-      <c r="N193" s="7"/>
-    </row>
-    <row r="194" spans="1:14">
+    </row>
+    <row r="194" spans="1:13">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -4081,9 +3869,8 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c r="M194" s="7"/>
-      <c r="N194" s="7"/>
-    </row>
-    <row r="195" spans="1:14">
+    </row>
+    <row r="195" spans="1:13">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -4097,9 +3884,8 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
-      <c r="N195" s="7"/>
-    </row>
-    <row r="196" spans="1:14">
+    </row>
+    <row r="196" spans="1:13">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -4113,9 +3899,8 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
-      <c r="N196" s="7"/>
-    </row>
-    <row r="197" spans="1:14">
+    </row>
+    <row r="197" spans="1:13">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -4129,9 +3914,8 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
-      <c r="N197" s="7"/>
-    </row>
-    <row r="198" spans="1:14">
+    </row>
+    <row r="198" spans="1:13">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -4145,9 +3929,8 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
-      <c r="N198" s="7"/>
-    </row>
-    <row r="199" spans="1:14">
+    </row>
+    <row r="199" spans="1:13">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -4161,9 +3944,8 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
-      <c r="N199" s="7"/>
-    </row>
-    <row r="200" spans="1:14">
+    </row>
+    <row r="200" spans="1:13">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -4177,9 +3959,8 @@
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
-      <c r="N200" s="7"/>
-    </row>
-    <row r="201" spans="1:14">
+    </row>
+    <row r="201" spans="1:13">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -4193,9 +3974,8 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
-      <c r="N201" s="7"/>
-    </row>
-    <row r="202" spans="1:14">
+    </row>
+    <row r="202" spans="1:13">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -4209,9 +3989,8 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
-      <c r="N202" s="7"/>
-    </row>
-    <row r="203" spans="1:14">
+    </row>
+    <row r="203" spans="1:13">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -4225,9 +4004,8 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
-      <c r="N203" s="7"/>
-    </row>
-    <row r="204" spans="1:14">
+    </row>
+    <row r="204" spans="1:13">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -4241,15 +4019,11 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
-      <c r="N204" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N201"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="关系类型" prompt="二选一，纯事实：已联系=默认（按可信度建 Me 边）；未联系=不建 Me 边，靠他人引荐。" sqref="N2:N2001">
-      <formula1>"已联系,未联系"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可信度" prompt="0-5 整数；未联系的人填 0" sqref="H2:H2001">
+  <autoFilter ref="A1:M201"/>
+  <dataValidations count="2">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可信度（0-5）" prompt="整数 0-5，单列承载两件事：&#10;  0  = 未联系（不建 Me 边，靠他人引荐到达）&#10;  1  = 点头之交&#10;  3  = 普通朋友&#10;  5  = 核心铁磁&#10;留空被当成 3，所以未联系的人务必显式填 0。" sqref="H2:H2001">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -4275,36 +4049,36 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="8">
         <v>3</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5149,7 +4923,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -5158,22 +4932,22 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="50" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="32" customHeight="1">
@@ -5181,39 +4955,39 @@
         <v>0</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="32" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="32" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="56" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="32" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="32" customHeight="1">
@@ -5221,39 +4995,39 @@
         <v>5</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="56" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="56" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="56" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="32" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="32" customHeight="1">
@@ -5261,15 +5035,15 @@
         <v>10</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="56" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="32" customHeight="1">
@@ -5277,95 +5051,87 @@
         <v>12</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="56" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="36" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="36" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="36" customHeight="1">
       <c r="A21" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="52" customHeight="1">
+      <c r="A22" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="36" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="52" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="52" customHeight="1">
       <c r="A24" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="76" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="52" customHeight="1">
-      <c r="A25" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="76" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="76" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="76" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="76" customHeight="1">
-      <c r="A29" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
